--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_arica_y_parinacota_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:14</t>
+    <t xml:space="preserve">2026-09-29 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_arica_y_parinacota_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:13</t>
+    <t xml:space="preserve">2026-09-29 18:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,10 +487,10 @@
         <v>23.15</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>160.83</v>
+        <v>160.82</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>137.67</v>
+        <v>137.68</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>31.95</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>38.87</v>
+        <v>38.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_arica_y_parinacota_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:41</t>
+    <t xml:space="preserve">2026-10-05 04:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,7 +487,7 @@
         <v>23.15</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>160.82</v>
+        <v>160.83</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>137.68</v>
@@ -501,7 +501,7 @@
         <v>-6.92</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>31.95</v>
+        <v>31.96</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>38.88</v>
